--- a/data/dividends_info_20260515.xlsx
+++ b/data/dividends_info_20260515.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>52.59000015258789</v>
+        <v>52.83000183105469</v>
       </c>
       <c r="I2" t="n">
-        <v>0.171135196308934</v>
+        <v>0.1703577453731905</v>
       </c>
       <c r="J2" t="n">
         <v>304</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>57</v>
+        <v>56.34999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.228070175438597</v>
+        <v>1.242236058482729</v>
       </c>
       <c r="J3" t="n">
         <v>283</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4779999852180481</v>
+        <v>0.4819999933242798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8368201095603234</v>
+        <v>0.8298755301660101</v>
       </c>
       <c r="J5" t="n">
         <v>213</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>52.59000015258789</v>
+        <v>52.83000183105469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.171135196308934</v>
+        <v>0.1703577453731905</v>
       </c>
       <c r="J6" t="n">
         <v>213</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.075000047683716</v>
+        <v>2.085000038146973</v>
       </c>
       <c r="I7" t="n">
-        <v>3.710843288218411</v>
+        <v>3.693045495981532</v>
       </c>
       <c r="J7" t="n">
         <v>192</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.56500053405762</v>
+        <v>23.52000045776367</v>
       </c>
       <c r="I8" t="n">
-        <v>1.145767001404388</v>
+        <v>1.147959161331037</v>
       </c>
       <c r="J8" t="n">
         <v>192</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.860000133514404</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I9" t="n">
-        <v>3.412969205515265</v>
+        <v>3.418803474537181</v>
       </c>
       <c r="J9" t="n">
         <v>185</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6.5</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="I10" t="n">
-        <v>0.923076923076923</v>
+        <v>0.909090922226919</v>
       </c>
       <c r="J10" t="n">
         <v>157</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4779999852180481</v>
+        <v>0.4819999933242798</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8368201095603234</v>
+        <v>0.8298755301660101</v>
       </c>
       <c r="J11" t="n">
         <v>157</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.199999809265137</v>
+        <v>5.300000190734863</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9615384968074835</v>
+        <v>0.9433961924644259</v>
       </c>
       <c r="J12" t="n">
         <v>143</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.96999979019165</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7615230810218038</v>
       </c>
       <c r="J13" t="n">
         <v>136</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.56500053405762</v>
+        <v>23.52000045776367</v>
       </c>
       <c r="I14" t="n">
-        <v>1.145767001404388</v>
+        <v>1.147959161331037</v>
       </c>
       <c r="J14" t="n">
         <v>129</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>52.59000015258789</v>
+        <v>52.83000183105469</v>
       </c>
       <c r="I15" t="n">
-        <v>0.171135196308934</v>
+        <v>0.1703577453731905</v>
       </c>
       <c r="J15" t="n">
         <v>129</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4.400000095367432</v>
+        <v>4.420000076293945</v>
       </c>
       <c r="I16" t="n">
-        <v>6.81818167040171</v>
+        <v>6.787330199585476</v>
       </c>
       <c r="J16" t="n">
         <v>122</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.4779999852180481</v>
+        <v>0.4819999933242798</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8368201095603234</v>
+        <v>0.8298755301660101</v>
       </c>
       <c r="J17" t="n">
         <v>101</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.96999979019165</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7615230810218038</v>
       </c>
       <c r="J18" t="n">
         <v>80</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.849999904632568</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I19" t="n">
-        <v>4.273504343171475</v>
+        <v>4.280821805958635</v>
       </c>
       <c r="J19" t="n">
         <v>73</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9.579000473022461</v>
+        <v>9.484000205993652</v>
       </c>
       <c r="I20" t="n">
-        <v>2.714270666675959</v>
+        <v>2.741459240328637</v>
       </c>
       <c r="J20" t="n">
         <v>66</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>15.35999965667725</v>
+        <v>15.38000011444092</v>
       </c>
       <c r="I21" t="n">
-        <v>3.906250087311494</v>
+        <v>3.901170322077145</v>
       </c>
       <c r="J21" t="n">
         <v>66</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.628000020980835</v>
+        <v>3.608000040054321</v>
       </c>
       <c r="I22" t="n">
-        <v>6.063947043212052</v>
+        <v>6.097560907917499</v>
       </c>
       <c r="J22" t="n">
         <v>66</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.4779999852180481</v>
+        <v>0.4819999933242798</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8368201095603234</v>
+        <v>0.8298755301660101</v>
       </c>
       <c r="J23" t="n">
         <v>66</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.159999847412109</v>
+        <v>6.170000076293945</v>
       </c>
       <c r="I24" t="n">
-        <v>3.896103992613359</v>
+        <v>3.889789254980977</v>
       </c>
       <c r="J24" t="n">
         <v>66</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>18.20000076293945</v>
+        <v>18.5</v>
       </c>
       <c r="I25" t="n">
-        <v>2.06593397933063</v>
+        <v>2.032432432432433</v>
       </c>
       <c r="J25" t="n">
         <v>66</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.28000020980835</v>
+        <v>4.144999980926514</v>
       </c>
       <c r="I26" t="n">
-        <v>2.803738180315963</v>
+        <v>2.895054295589573</v>
       </c>
       <c r="J26" t="n">
         <v>59</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4.190000057220459</v>
+        <v>4.340000152587891</v>
       </c>
       <c r="I29" t="n">
-        <v>1.67064436859307</v>
+        <v>1.612903169099195</v>
       </c>
       <c r="J29" t="n">
         <v>52</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>32.29999923706055</v>
+        <v>31.04999923706055</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4643962957989553</v>
+        <v>0.4830917993098162</v>
       </c>
       <c r="J30" t="n">
         <v>52</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>22.60000038146973</v>
+        <v>22.52000045776367</v>
       </c>
       <c r="I32" t="n">
-        <v>4.203539752056497</v>
+        <v>4.2184723831677</v>
       </c>
       <c r="J32" t="n">
         <v>38</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>31.25</v>
+        <v>30.75</v>
       </c>
       <c r="I33" t="n">
-        <v>0.624</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="J33" t="n">
         <v>38</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.850000023841858</v>
+        <v>1.894999980926514</v>
       </c>
       <c r="I34" t="n">
-        <v>1.783783760795287</v>
+        <v>1.741424819638545</v>
       </c>
       <c r="J34" t="n">
         <v>38</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4.861999988555908</v>
+        <v>4.868000030517578</v>
       </c>
       <c r="I35" t="n">
-        <v>5.964623625721863</v>
+        <v>5.957271942933132</v>
       </c>
       <c r="J35" t="n">
         <v>38</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3.812000036239624</v>
+        <v>3.79800009727478</v>
       </c>
       <c r="I36" t="n">
-        <v>4.19727173344503</v>
+        <v>4.212743441339207</v>
       </c>
       <c r="J36" t="n">
         <v>38</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.640000104904175</v>
+        <v>2.644000053405762</v>
       </c>
       <c r="I37" t="n">
-        <v>5.249999791383752</v>
+        <v>5.24205738277002</v>
       </c>
       <c r="J37" t="n">
         <v>38</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>49.8849983215332</v>
+        <v>48.9900016784668</v>
       </c>
       <c r="I38" t="n">
-        <v>1.262904723258367</v>
+        <v>1.285976685885504</v>
       </c>
       <c r="J38" t="n">
         <v>38</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5.184999942779541</v>
+        <v>5.179999828338623</v>
       </c>
       <c r="I39" t="n">
-        <v>2.700096461813069</v>
+        <v>2.702702792268278</v>
       </c>
       <c r="J39" t="n">
         <v>38</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>19.29999923706055</v>
+        <v>18.5</v>
       </c>
       <c r="I40" t="n">
-        <v>4.041450936962817</v>
+        <v>4.216216216216216</v>
       </c>
       <c r="J40" t="n">
         <v>38</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>24.17000007629395</v>
+        <v>24.22999954223633</v>
       </c>
       <c r="I41" t="n">
-        <v>3.516756298373719</v>
+        <v>3.508047940811263</v>
       </c>
       <c r="J41" t="n">
         <v>38</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>52.59000015258789</v>
+        <v>52.83000183105469</v>
       </c>
       <c r="I42" t="n">
-        <v>0.171135196308934</v>
+        <v>0.1703577453731905</v>
       </c>
       <c r="J42" t="n">
         <v>38</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6.277999877929688</v>
+        <v>6.196000099182129</v>
       </c>
       <c r="I44" t="n">
-        <v>2.887862432705044</v>
+        <v>2.926081295962722</v>
       </c>
       <c r="J44" t="n">
         <v>38</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>8.460000038146973</v>
+        <v>8.439999580383301</v>
       </c>
       <c r="I45" t="n">
-        <v>3.073286038151707</v>
+        <v>3.080568873537695</v>
       </c>
       <c r="J45" t="n">
         <v>38</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>9.824000358581543</v>
+        <v>9.666000366210938</v>
       </c>
       <c r="I46" t="n">
-        <v>2.81962530424821</v>
+        <v>2.86571476831615</v>
       </c>
       <c r="J46" t="n">
         <v>38</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.144999980926514</v>
+        <v>1.149999976158142</v>
       </c>
       <c r="I47" t="n">
-        <v>1.179039320950559</v>
+        <v>1.173913067815886</v>
       </c>
       <c r="J47" t="n">
         <v>31</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>3.279999971389771</v>
+        <v>3.164000034332275</v>
       </c>
       <c r="I48" t="n">
-        <v>3.353658565838092</v>
+        <v>3.476611845967132</v>
       </c>
       <c r="J48" t="n">
         <v>31</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.079999923706055</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="I50" t="n">
-        <v>5.194805323484478</v>
+        <v>5.280528102665716</v>
       </c>
       <c r="J50" t="n">
         <v>24</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.8799999952316284</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="I51" t="n">
-        <v>2.840909106302853</v>
+        <v>2.777777851363761</v>
       </c>
       <c r="J51" t="n">
         <v>24</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>27.25</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="I52" t="n">
-        <v>4.073394495412844</v>
+        <v>4.065934179562696</v>
       </c>
       <c r="J52" t="n">
         <v>20</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8859999775886536</v>
+        <v>0.8790000081062317</v>
       </c>
       <c r="I53" t="n">
-        <v>3.386004600321582</v>
+        <v>3.412969251801684</v>
       </c>
       <c r="J53" t="n">
         <v>17</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.5120000243186951</v>
+        <v>0.5059999823570251</v>
       </c>
       <c r="I54" t="n">
-        <v>4.492187286632553</v>
+        <v>4.545454703943365</v>
       </c>
       <c r="J54" t="n">
         <v>17</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>2.515000104904175</v>
+        <v>2.470000028610229</v>
       </c>
       <c r="I57" t="n">
-        <v>7.157057355544653</v>
+        <v>7.287449308301378</v>
       </c>
       <c r="J57" t="n">
         <v>10</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>14.3100004196167</v>
+        <v>14.39999961853027</v>
       </c>
       <c r="I59" t="n">
-        <v>1.747029997688123</v>
+        <v>1.73611115710235</v>
       </c>
       <c r="J59" t="n">
         <v>10</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>3.339999914169312</v>
+        <v>3.319999933242798</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8982036158962379</v>
+        <v>0.9036144760008356</v>
       </c>
       <c r="J60" t="n">
         <v>10</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>4.090000152587891</v>
+        <v>4</v>
       </c>
       <c r="I61" t="n">
-        <v>3.667481525766927</v>
+        <v>3.75</v>
       </c>
       <c r="J61" t="n">
         <v>10</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>13.60000038146973</v>
+        <v>13.80000019073486</v>
       </c>
       <c r="I62" t="n">
-        <v>4.264705762731166</v>
+        <v>4.202898492634835</v>
       </c>
       <c r="J62" t="n">
         <v>10</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2.289999961853027</v>
+        <v>2.276000022888184</v>
       </c>
       <c r="I63" t="n">
-        <v>4.541484791809562</v>
+        <v>4.569419989197836</v>
       </c>
       <c r="J63" t="n">
         <v>3</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>10.94999980926514</v>
+        <v>10.93000030517578</v>
       </c>
       <c r="I64" t="n">
-        <v>2.648401872615759</v>
+        <v>2.65324786736441</v>
       </c>
       <c r="J64" t="n">
         <v>3</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.075000047683716</v>
+        <v>2.085000038146973</v>
       </c>
       <c r="I65" t="n">
-        <v>3.710843288218411</v>
+        <v>3.693045495981532</v>
       </c>
       <c r="J65" t="n">
         <v>3</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>38.56000137329102</v>
+        <v>38.63000106811523</v>
       </c>
       <c r="I66" t="n">
-        <v>4.25311188172302</v>
+        <v>4.245405008165111</v>
       </c>
       <c r="J66" t="n">
         <v>3</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>35.66999816894531</v>
+        <v>35.2400016784668</v>
       </c>
       <c r="I67" t="n">
-        <v>5.606952909073097</v>
+        <v>5.675368628662945</v>
       </c>
       <c r="J67" t="n">
         <v>3</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>3.766000032424927</v>
+        <v>3.684000015258789</v>
       </c>
       <c r="I68" t="n">
-        <v>2.655337204965716</v>
+        <v>2.714440813947047</v>
       </c>
       <c r="J68" t="n">
         <v>3</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>29.78000068664551</v>
+        <v>30.25</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4985224868264531</v>
+        <v>0.4907768595041322</v>
       </c>
       <c r="J69" t="n">
         <v>3</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>21.1200008392334</v>
+        <v>20.79999923706055</v>
       </c>
       <c r="I70" t="n">
-        <v>4.356060432966316</v>
+        <v>4.423077085314424</v>
       </c>
       <c r="J70" t="n">
         <v>3</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>10.89000034332275</v>
+        <v>10.86999988555908</v>
       </c>
       <c r="I71" t="n">
-        <v>2.754820849789469</v>
+        <v>2.759889633472337</v>
       </c>
       <c r="J71" t="n">
         <v>3</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>81.80000305175781</v>
+        <v>81.12000274658203</v>
       </c>
       <c r="I72" t="n">
-        <v>1.271393595599201</v>
+        <v>1.282051238643258</v>
       </c>
       <c r="J72" t="n">
         <v>3</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>45.43999862670898</v>
+        <v>44.79999923706055</v>
       </c>
       <c r="I73" t="n">
-        <v>1.540493004303372</v>
+        <v>1.562500026609217</v>
       </c>
       <c r="J73" t="n">
         <v>3</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>57</v>
+        <v>56.34999847412109</v>
       </c>
       <c r="I74" t="n">
-        <v>3.859649122807018</v>
+        <v>3.904170469517149</v>
       </c>
       <c r="J74" t="n">
         <v>3</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>9.413999557495117</v>
+        <v>9.371000289916992</v>
       </c>
       <c r="I75" t="n">
-        <v>9.135330788445769</v>
+        <v>9.177248675633301</v>
       </c>
       <c r="J75" t="n">
         <v>3</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>12.35599994659424</v>
+        <v>12.21199989318848</v>
       </c>
       <c r="I76" t="n">
-        <v>4.532211091133554</v>
+        <v>4.585653495725568</v>
       </c>
       <c r="J76" t="n">
         <v>3</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>9.079999923706055</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="I78" t="n">
-        <v>3.30396478547054</v>
+        <v>3.267973747570104</v>
       </c>
       <c r="J78" t="n">
         <v>3</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>98.69999694824219</v>
+        <v>98</v>
       </c>
       <c r="I80" t="n">
-        <v>2.087132789963767</v>
+        <v>2.102040816326531</v>
       </c>
       <c r="J80" t="n">
         <v>3</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>15.43000030517578</v>
+        <v>15.56999969482422</v>
       </c>
       <c r="I81" t="n">
-        <v>4.860660953768243</v>
+        <v>4.81695577842121</v>
       </c>
       <c r="J81" t="n">
         <v>3</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>14.48999977111816</v>
+        <v>14.14000034332275</v>
       </c>
       <c r="I82" t="n">
-        <v>2.07039340744482</v>
+        <v>2.121640683988153</v>
       </c>
       <c r="J82" t="n">
         <v>3</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>53</v>
+        <v>53.59999847412109</v>
       </c>
       <c r="I83" t="n">
-        <v>1.60377358490566</v>
+        <v>1.585820940667364</v>
       </c>
       <c r="J83" t="n">
         <v>3</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>35.91999816894531</v>
+        <v>36.7400016784668</v>
       </c>
       <c r="I84" t="n">
-        <v>2.366369831095561</v>
+        <v>2.313554603069554</v>
       </c>
       <c r="J84" t="n">
         <v>3</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>69.90000152587891</v>
+        <v>70.45999908447266</v>
       </c>
       <c r="I85" t="n">
-        <v>1.859799673278554</v>
+        <v>1.845018474157889</v>
       </c>
       <c r="J85" t="n">
         <v>3</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>7.980000019073486</v>
+        <v>7.960000038146973</v>
       </c>
       <c r="I86" t="n">
-        <v>7.518796974510066</v>
+        <v>7.53768840608794</v>
       </c>
       <c r="J86" t="n">
         <v>3</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>6.25</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="I87" t="n">
-        <v>7.519999999999999</v>
+        <v>7.401574914310108</v>
       </c>
       <c r="J87" t="n">
         <v>3</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>5.860000133514404</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I88" t="n">
-        <v>3.412969205515265</v>
+        <v>3.418803474537181</v>
       </c>
       <c r="J88" t="n">
         <v>3</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>23.68000030517578</v>
+        <v>23.3799991607666</v>
       </c>
       <c r="I89" t="n">
-        <v>4.222972918549448</v>
+        <v>4.277160119312901</v>
       </c>
       <c r="J89" t="n">
         <v>3</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>4.800000190734863</v>
+        <v>4.75</v>
       </c>
       <c r="I90" t="n">
-        <v>4.479166488680582</v>
+        <v>4.526315789473684</v>
       </c>
       <c r="J90" t="n">
         <v>3</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>23.56500053405762</v>
+        <v>23.52000045776367</v>
       </c>
       <c r="I91" t="n">
-        <v>1.145767001404388</v>
+        <v>1.147959161331037</v>
       </c>
       <c r="J91" t="n">
         <v>3</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>9.699999809265137</v>
+        <v>9.539999961853027</v>
       </c>
       <c r="I92" t="n">
-        <v>2.061855710646161</v>
+        <v>2.096436067083091</v>
       </c>
       <c r="J92" t="n">
         <v>3</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>8.895000457763672</v>
+        <v>9.064999580383301</v>
       </c>
       <c r="I93" t="n">
-        <v>2.698144886440392</v>
+        <v>2.647545627242621</v>
       </c>
       <c r="J93" t="n">
         <v>3</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>21.29000091552734</v>
+        <v>21.34000015258789</v>
       </c>
       <c r="I94" t="n">
-        <v>3.710662123193394</v>
+        <v>3.701968108487558</v>
       </c>
       <c r="J94" t="n">
         <v>3</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>5.260000228881836</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="I95" t="n">
-        <v>1.768060759567112</v>
+        <v>1.761363566373337</v>
       </c>
       <c r="J95" t="n">
         <v>3</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>6.5</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="I96" t="n">
-        <v>0.923076923076923</v>
+        <v>0.909090922226919</v>
       </c>
       <c r="J96" t="n">
         <v>3</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>35.7400016784668</v>
+        <v>33.72000122070312</v>
       </c>
       <c r="I97" t="n">
-        <v>0.979294861675604</v>
+        <v>1.037959630277563</v>
       </c>
       <c r="J97" t="n">
         <v>3</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>7.135000228881836</v>
+        <v>7.025000095367432</v>
       </c>
       <c r="I98" t="n">
-        <v>7.768745370970609</v>
+        <v>7.890391351959238</v>
       </c>
       <c r="J98" t="n">
         <v>3</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>2.25</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I99" t="n">
-        <v>2.666666666666667</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J99" t="n">
         <v>3</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>13.05000019073486</v>
+        <v>12.80000019073486</v>
       </c>
       <c r="I100" t="n">
-        <v>1.532567027408892</v>
+        <v>1.562499976716936</v>
       </c>
       <c r="J100" t="n">
         <v>3</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>6.985000133514404</v>
+        <v>6.934999942779541</v>
       </c>
       <c r="I101" t="n">
-        <v>1.474588375536322</v>
+        <v>1.485219911317226</v>
       </c>
       <c r="J101" t="n">
         <v>3</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>5.675000190734863</v>
+        <v>5.735000133514404</v>
       </c>
       <c r="I102" t="n">
-        <v>3.348017508619619</v>
+        <v>3.312990332636106</v>
       </c>
       <c r="J102" t="n">
         <v>3</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>10.26500034332275</v>
+        <v>10.13000011444092</v>
       </c>
       <c r="I103" t="n">
-        <v>4.208475261094465</v>
+        <v>4.264560662582404</v>
       </c>
       <c r="J103" t="n">
         <v>3</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>26.18000030517578</v>
+        <v>26</v>
       </c>
       <c r="I104" t="n">
-        <v>1.680672249316254</v>
+        <v>1.692307692307692</v>
       </c>
       <c r="J104" t="n">
         <v>3</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1.009999990463257</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
-        <v>2.970297057749466</v>
+        <v>3</v>
       </c>
       <c r="J105" t="n">
         <v>3</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>8.399999618530273</v>
+        <v>8.210000038146973</v>
       </c>
       <c r="I106" t="n">
-        <v>5.595238349335005</v>
+        <v>5.72472591737138</v>
       </c>
       <c r="J106" t="n">
         <v>3</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>49.81999969482422</v>
+        <v>49.70999908447266</v>
       </c>
       <c r="I107" t="n">
-        <v>2.81011643632235</v>
+        <v>2.816334793370177</v>
       </c>
       <c r="J107" t="n">
         <v>3</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>3.773999929428101</v>
+        <v>3.697000026702881</v>
       </c>
       <c r="I108" t="n">
-        <v>7.949125744829068</v>
+        <v>8.114687525916816</v>
       </c>
       <c r="J108" t="n">
         <v>3</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>13.14999961853027</v>
+        <v>13.10000038146973</v>
       </c>
       <c r="I109" t="n">
-        <v>0.9125475549892977</v>
+        <v>0.9160305076764956</v>
       </c>
       <c r="J109" t="n">
         <v>3</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.579999923706055</v>
+        <v>3.650000095367432</v>
       </c>
       <c r="I110" t="n">
-        <v>4.748603453153546</v>
+        <v>4.657534124882996</v>
       </c>
       <c r="J110" t="n">
         <v>3</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>22.29999923706055</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="I111" t="n">
-        <v>3.139013560308399</v>
+        <v>3.271028095691504</v>
       </c>
       <c r="J111" t="n">
         <v>3</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>2.440000057220459</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="I112" t="n">
-        <v>1.434426195869457</v>
+        <v>1.495726550589419</v>
       </c>
       <c r="J112" t="n">
         <v>3</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>5.880000114440918</v>
+        <v>5.909999847412109</v>
       </c>
       <c r="I113" t="n">
-        <v>5.612244788729517</v>
+        <v>5.583756489342407</v>
       </c>
       <c r="J113" t="n">
         <v>3</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>0.984000027179718</v>
+        <v>0.9959999918937683</v>
       </c>
       <c r="I114" t="n">
-        <v>7.113820941715806</v>
+        <v>7.028112506999507</v>
       </c>
       <c r="J114" t="n">
         <v>3</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>51.70000076293945</v>
+        <v>51.5</v>
       </c>
       <c r="I115" t="n">
-        <v>1.373307523254342</v>
+        <v>1.378640776699029</v>
       </c>
       <c r="J115" t="n">
         <v>3</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>92.40000152587891</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="I116" t="n">
-        <v>1.461038936911597</v>
+        <v>1.381781005290286</v>
       </c>
       <c r="J116" t="n">
         <v>3</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>7.039999961853027</v>
+        <v>7.019999980926514</v>
       </c>
       <c r="I117" t="n">
-        <v>1.136363642521141</v>
+        <v>1.13960114269746</v>
       </c>
       <c r="J117" t="n">
         <v>3</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>4.692999839782715</v>
+        <v>4.65500020980835</v>
       </c>
       <c r="I119" t="n">
-        <v>3.622416488466596</v>
+        <v>3.651986946032792</v>
       </c>
       <c r="J119" t="n">
         <v>3</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>58.40000152587891</v>
+        <v>59.09999847412109</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7705479250725544</v>
+        <v>0.7614213394557828</v>
       </c>
       <c r="J121" t="n">
         <v>3</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>5.159999847412109</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7751938213730989</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J122" t="n">
         <v>3</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>21.28000068664551</v>
+        <v>21.29999923706055</v>
       </c>
       <c r="I125" t="n">
-        <v>1.78571422809433</v>
+        <v>1.78403762258745</v>
       </c>
       <c r="J125" t="n">
         <v>3</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>26.8700008392334</v>
+        <v>26.65999984741211</v>
       </c>
       <c r="I126" t="n">
-        <v>2.23297350673666</v>
+        <v>2.250562653541208</v>
       </c>
       <c r="J126" t="n">
         <v>3</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>35.90000152587891</v>
+        <v>37.09999847412109</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9749303206789522</v>
+        <v>0.9433962652158614</v>
       </c>
       <c r="J127" t="n">
         <v>3</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>2.785000085830688</v>
+        <v>2.815000057220459</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3590664162230098</v>
+        <v>0.3552397796351747</v>
       </c>
       <c r="J129" t="n">
         <v>3</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>22.26000022888184</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="I130" t="n">
-        <v>5.03144648914615</v>
+        <v>5.05643349566033</v>
       </c>
       <c r="J130" t="n">
         <v>3</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>1.590000033378601</v>
+        <v>1.559999942779541</v>
       </c>
       <c r="I131" t="n">
-        <v>6.289308044070249</v>
+        <v>6.410256645383224</v>
       </c>
       <c r="J131" t="n">
         <v>3</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>8.760000228881836</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I132" t="n">
-        <v>2.968036452131321</v>
+        <v>3.023255679851103</v>
       </c>
       <c r="J132" t="n">
         <v>3</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>2.114000082015991</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I133" t="n">
-        <v>4.366130388792568</v>
+        <v>4.195454454520519</v>
       </c>
       <c r="J133" t="n">
         <v>3</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>8.619999885559082</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I134" t="n">
-        <v>4.060324879891799</v>
+        <v>4.069767261338023</v>
       </c>
       <c r="J134" t="n">
         <v>-4</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>5.050000190734863</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="I135" t="n">
-        <v>1.900990027210877</v>
+        <v>1.846153913870368</v>
       </c>
       <c r="J135" t="n">
         <v>-4</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>6.099999904632568</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I136" t="n">
-        <v>4.918032863773797</v>
+        <v>4.958677529621045</v>
       </c>
       <c r="J136" t="n">
         <v>-4</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>11.60000038146973</v>
+        <v>11.5</v>
       </c>
       <c r="I137" t="n">
-        <v>1.724137874335655</v>
+        <v>1.739130434782609</v>
       </c>
       <c r="J137" t="n">
         <v>-4</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>18.8799991607666</v>
+        <v>18.81999969482422</v>
       </c>
       <c r="I139" t="n">
-        <v>2.648305202465369</v>
+        <v>2.656748183356812</v>
       </c>
       <c r="J139" t="n">
         <v>-4</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>15.65999984741211</v>
+        <v>15.03999996185303</v>
       </c>
       <c r="I141" t="n">
-        <v>3.192848051544697</v>
+        <v>3.324468093538457</v>
       </c>
       <c r="J141" t="n">
         <v>-4</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>3.759999990463257</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="I142" t="n">
-        <v>2.659574474830765</v>
+        <v>2.645502665526042</v>
       </c>
       <c r="J142" t="n">
         <v>-4</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1.200000047683716</v>
+        <v>1.139999985694885</v>
       </c>
       <c r="I146" t="n">
-        <v>2.49999990065893</v>
+        <v>2.631578980390385</v>
       </c>
       <c r="J146" t="n">
         <v>-4</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>7</v>
+        <v>6.96999979019165</v>
       </c>
       <c r="I149" t="n">
-        <v>3.142857142857143</v>
+        <v>3.156384600033837</v>
       </c>
       <c r="J149" t="n">
         <v>-4</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>29.35000038146973</v>
+        <v>28.04999923706055</v>
       </c>
       <c r="I150" t="n">
-        <v>2.07836453857468</v>
+        <v>2.174688116190922</v>
       </c>
       <c r="J150" t="n">
         <v>-11</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>2.880000114440918</v>
+        <v>2.859999895095825</v>
       </c>
       <c r="I151" t="n">
-        <v>5.208333126372769</v>
+        <v>5.244755437131728</v>
       </c>
       <c r="J151" t="n">
         <v>-11</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>10.55000019073486</v>
+        <v>11.10000038146973</v>
       </c>
       <c r="I152" t="n">
-        <v>6.635070970091056</v>
+        <v>6.306306089579743</v>
       </c>
       <c r="J152" t="n">
         <v>-11</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>8.720000267028809</v>
+        <v>8.649999618530273</v>
       </c>
       <c r="I153" t="n">
-        <v>5.854357618889662</v>
+        <v>5.901734364315953</v>
       </c>
       <c r="J153" t="n">
         <v>-11</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>8.350000381469727</v>
+        <v>8.340000152587891</v>
       </c>
       <c r="I154" t="n">
-        <v>3.233532786407801</v>
+        <v>3.237410012711084</v>
       </c>
       <c r="J154" t="n">
         <v>-11</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>7.014999866485596</v>
+        <v>7.045000076293945</v>
       </c>
       <c r="I155" t="n">
-        <v>4.989308719336362</v>
+        <v>4.968062401840585</v>
       </c>
       <c r="J155" t="n">
         <v>-11</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>17.10000038146973</v>
+        <v>16.89999961853027</v>
       </c>
       <c r="I157" t="n">
-        <v>4.385964814437848</v>
+        <v>4.437869922657575</v>
       </c>
       <c r="J157" t="n">
         <v>-11</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>10.5</v>
+        <v>10.39999961853027</v>
       </c>
       <c r="I158" t="n">
-        <v>4.095238095238095</v>
+        <v>4.134615536272179</v>
       </c>
       <c r="J158" t="n">
         <v>-11</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>4.079999923706055</v>
+        <v>4.050000190734863</v>
       </c>
       <c r="I159" t="n">
-        <v>3.676470656983444</v>
+        <v>3.703703529277682</v>
       </c>
       <c r="J159" t="n">
         <v>-11</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>11.85999965667725</v>
+        <v>11.77999973297119</v>
       </c>
       <c r="I160" t="n">
-        <v>1.662470537163909</v>
+        <v>1.673760649146206</v>
       </c>
       <c r="J160" t="n">
         <v>-11</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>65.59999847412109</v>
+        <v>66.40000152587891</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7164634312993359</v>
+        <v>0.7078313090351677</v>
       </c>
       <c r="J162" t="n">
         <v>-11</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>89.59999847412109</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="I163" t="n">
-        <v>1.339285737093614</v>
+        <v>1.334816440080442</v>
       </c>
       <c r="J163" t="n">
         <v>-11</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>23.95000076293945</v>
+        <v>23.20000076293945</v>
       </c>
       <c r="I164" t="n">
-        <v>1.127348607093999</v>
+        <v>1.163793065176567</v>
       </c>
       <c r="J164" t="n">
         <v>-11</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>36.34999847412109</v>
+        <v>35.59999847412109</v>
       </c>
       <c r="I166" t="n">
-        <v>0.8253095257035046</v>
+        <v>0.8426966653329513</v>
       </c>
       <c r="J166" t="n">
         <v>-11</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>0.1684000045061111</v>
+        <v>0.1666000038385391</v>
       </c>
       <c r="I167" t="n">
-        <v>4.156769484971109</v>
+        <v>4.201680575460292</v>
       </c>
       <c r="J167" t="n">
         <v>-18</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>6.809999942779541</v>
+        <v>6.860000133514404</v>
       </c>
       <c r="I168" t="n">
-        <v>2.34948606966794</v>
+        <v>2.332361470640838</v>
       </c>
       <c r="J168" t="n">
         <v>-18</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>2.079999923706055</v>
+        <v>2.055000066757202</v>
       </c>
       <c r="I169" t="n">
-        <v>3.125000114624321</v>
+        <v>3.163016928878754</v>
       </c>
       <c r="J169" t="n">
         <v>-18</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>7.190000057220459</v>
+        <v>7.239999771118164</v>
       </c>
       <c r="I172" t="n">
-        <v>6.954102865380117</v>
+        <v>6.906077566391673</v>
       </c>
       <c r="J172" t="n">
         <v>-25</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>19.42499923706055</v>
+        <v>19.1200008392334</v>
       </c>
       <c r="I173" t="n">
-        <v>3.346203477629377</v>
+        <v>3.399581440740466</v>
       </c>
       <c r="J173" t="n">
         <v>-25</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>13.08500003814697</v>
+        <v>13.09500026702881</v>
       </c>
       <c r="I174" t="n">
-        <v>4.126862807991798</v>
+        <v>4.123711256116861</v>
       </c>
       <c r="J174" t="n">
         <v>-25</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>5.363999843597412</v>
+        <v>5.401999950408936</v>
       </c>
       <c r="I175" t="n">
-        <v>1.864280442128689</v>
+        <v>1.851166251721826</v>
       </c>
       <c r="J175" t="n">
         <v>-25</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>8.140000343322754</v>
+        <v>8.119999885559082</v>
       </c>
       <c r="I176" t="n">
-        <v>1.965601882698298</v>
+        <v>1.97044337752455</v>
       </c>
       <c r="J176" t="n">
         <v>-25</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>281.5</v>
+        <v>279.3999938964844</v>
       </c>
       <c r="I177" t="n">
-        <v>1.284191829484902</v>
+        <v>1.293843979588393</v>
       </c>
       <c r="J177" t="n">
         <v>-25</v>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>28</v>
+        <v>28.20000076293945</v>
       </c>
       <c r="I178" t="n">
-        <v>4.857142857142858</v>
+        <v>4.822694904984957</v>
       </c>
       <c r="J178" t="n">
         <v>-25</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>13.92500019073486</v>
+        <v>13.93000030517578</v>
       </c>
       <c r="I179" t="n">
-        <v>41.80682168947803</v>
+        <v>41.79181530840992</v>
       </c>
       <c r="J179" t="n">
         <v>-25</v>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>14.57999992370605</v>
+        <v>14.5</v>
       </c>
       <c r="I180" t="n">
-        <v>4.012345700008072</v>
+        <v>4.03448275862069</v>
       </c>
       <c r="J180" t="n">
         <v>-25</v>
@@ -8936,10 +8936,10 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>20.57999992370605</v>
+        <v>20.46999931335449</v>
       </c>
       <c r="I181" t="n">
-        <v>3.061224501144456</v>
+        <v>3.077674749060652</v>
       </c>
       <c r="J181" t="n">
         <v>-25</v>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>150.8999938964844</v>
+        <v>153.1499938964844</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5964214952966728</v>
+        <v>0.587659181108632</v>
       </c>
       <c r="J182" t="n">
         <v>-25</v>
@@ -9030,10 +9030,10 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>71.36000061035156</v>
+        <v>71.26000213623047</v>
       </c>
       <c r="I183" t="n">
-        <v>2.411434956953152</v>
+        <v>2.414818900384371</v>
       </c>
       <c r="J183" t="n">
         <v>-25</v>
@@ -10946,7 +10946,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10980,7 +10980,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11014,7 +11014,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11048,7 +11048,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11133,7 +11133,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11167,7 +11167,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11269,7 +11269,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Homizy SIIQ S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11279,14 +11279,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11303,7 +11303,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Homizy SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -11337,7 +11337,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11354,7 +11354,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11388,7 +11388,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11398,14 +11398,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -11447,104 +11447,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ESPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005573818</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-09-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4.400000095367432</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>6.81818167040171</v>
-      </c>
-      <c r="I2" t="n">
-        <v>122</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11555,163 +11460,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CROWDFUNDME S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DBA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OSAI Automation System S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Simone S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Tecno S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Telmes S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>